--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Rimozione veicoli.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Rimozione veicoli.xlsx
@@ -352,7 +352,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è considerato in stato in abbandono. 
+      <t xml:space="preserve"> è considerato in stato in abbandono.
 Per maggiori informazioni visita [questo sito](URL).</t>
     </r>
   </si>
@@ -431,7 +431,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è stato rimosso. 
+      <t xml:space="preserve"> è stato rimosso.
 Il tuo veicolo si trova presso il deposito in </t>
     </r>
     <r>
@@ -511,8 +511,8 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
-Potrai ritirarlo solo dopo avere pagato i costi di servizio e deposito. 
+      <t xml:space="preserve">.
+Potrai ritirarlo solo dopo avere pagato i costi di servizio e deposito.
 Per maggiori informazioni visita [questo sito](URL).</t>
     </r>
   </si>
@@ -550,7 +550,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
